--- a/static_content/jobs/jobs-processed.xlsx
+++ b/static_content/jobs/jobs-processed.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -429,52 +417,52 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>role</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>employer</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>z-index</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>css name</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>css RGB</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>css color</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>text color</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -913,7 +901,7 @@
       <c r="J10" t="inlineStr">
         <is>
           <t>• As a senior software engineer at [BigR.io]{https://shawn.beckerstudio.com/wp-content/uploads/2023/05/Bigr.io_-150x106.png} I used [Amazon microservices] for custom voice-based [natural language processing] applications.
-• Used [Apache ActiveMQ](https://activemq.apache.org/), [Swagger](https://swagger.io/), [JSON], [Jackson](http://wwwurl.com), [AOP](https://www.baeldung.com/spring-aop), [Eclipse], [Maven], [GitHub], [Jira], [PostgreSQL], and [Jenkins].
+• Used [Apache ActiveMQ](https://activemq.apache.org/), [Swagger](https://swagger.io/), [JSON], [Jackson], [AOP](https://www.baeldung.com/spring-aop), [Eclipse], [Maven], [GitHub], [Jira], [PostgreSQL], and [Jenkins].
 • [Java], [J2EE], [Servlets], [Spring], [SpringBoot], [JAX-RS], [Bash], [Linux], [JUnit], [JMeter], and [JProfile]</t>
         </is>
       </c>

--- a/static_content/jobs/jobs-processed.xlsx
+++ b/static_content/jobs/jobs-processed.xlsx
@@ -900,9 +900,9 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>• As a senior software engineer at [BigR.io]{https://shawn.beckerstudio.com/wp-content/uploads/2023/05/Bigr.io_-150x106.png} I used [Amazon microservices] for custom voice-based [natural language processing] applications.
-• Used [Apache ActiveMQ](https://activemq.apache.org/), [Swagger](https://swagger.io/), [JSON], [Jackson], [AOP](https://www.baeldung.com/spring-aop), [Eclipse], [Maven], [GitHub], [Jira], [PostgreSQL], and [Jenkins].
-• [Java], [J2EE], [Servlets], [Spring], [SpringBoot], [JAX-RS], [Bash], [Linux], [JUnit], [JMeter], and [JProfile]</t>
+          <t xml:space="preserve">• As a senior software engineer at {https://shawn.beckerstudio.com/wp-content/uploads/2023/05/Bigr.io_-150x106.png} I used [Amazon microservices] for custom voice-based [natural language processing] applications.
+• Used [Apache ActiveMQ](https://activemq.apache.org/), (https://swagger.io/), [http://JSON.com], [http://Jackson.com], [http://AOP.com](https://www.baeldung.com/spring-aop), [http://Eclipse.com], [http://Maven.com], [http://GitHub.com], [http://Jira.com], [http://PostgreSQL.com], and .
+• , , [http://Servlets.com], [http://Spring.com], , , [http://Bash.com], [http://Linux.com], [http://JUnit.com], , and </t>
         </is>
       </c>
     </row>
@@ -1048,13 +1048,13 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>• As co-founder and CTO, designed and led the development of a public website used by discerning home designers and builders called [HomePortfolio](https://HomePortfolio/). 
+          <t>• As co-founder and CTO, designed and led the development of a public website used by discerning home designers and builders called [http://HomePortfolio.com](https://HomePortfolio/). 
 • Hired a staff of  10 software and databases developers. 
 • Worked with data acquisition team to scan and tag over 700,000 premium home design products from over 2,000 manufactures and vendors.
 • Designed datamodel and data entry tools for category-specific product attribution. 
 • Helped extended the business model to provide online product selection tools for participating vendors and manufacturers.
 • Instrumental in raising over $70M in venture capital. 
-• Used [Oracle], [ATG Dyanamo]( https://docs.oracle.com/cd/E24152_01/Platform.10-1/ATGPersBusinessGuide/html/s0102dynamoapplicationframework01.html), [Java], [Akamai]{https://www.hiclipart.com/free-transparent-background-png-clipart-zkmsn}(https://www.akamai.com/), [WebTrends](https://www.webtrends.com/), [FileMakerPro], [ImageMagik](https://imagemagick.org/index.php), [Bash], [Linux], [HTML], [JavaScript], [CSS], and [Omnigraffle](https://www.omnigroup.com/omnigraffle) for data modeling and workflow designs.</t>
+• Used [http://Oracle.com], [ATG Dyanamo]( https://docs.oracle.com/cd/E24152_01/Platform.10-1/ATGPersBusinessGuide/html/s0102dynamoapplicationframework01.html), , {https://www.hiclipart.com/free-transparent-background-png-clipart-zkmsn}(https://www.akamai.com/), [http://WebTrends.com](https://www.webtrends.com/), [http://FileMakerPro.com], (https://imagemagick.org/index.php), [http://Bash.com], [http://Linux.com], , [http://JavaScript.com], , and [http://Omnigraffle.com](https://www.omnigroup.com/omnigraffle) for data modeling and workflow designs.</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1102,7 @@
         <is>
           <t>• As lead software developer, built a CD-ROM-based home design application for selecting premium home design products for previewing in the context of images of any household rooms. 
 • Built the prototype using Adobe Photoshop and [Macromedia Director](https://macromedia.fandom.com/wiki/Macromedia_Director).
-• Built the actual application using using [Bash], [Linux], [Java] and [Marimba Bongo](https://www.thriftbooks.com/w/official-marimba-guide-to-bongo_danny-goodman/2574616/#edition=58026223&amp;idiq=42367912) widget layout tool.
+• Built the actual application using using [http://Bash.com], [http://Linux.com],  and [Marimba Bongo](https://www.thriftbooks.com/w/official-marimba-guide-to-bongo_danny-goodman/2574616/#edition=58026223&amp;idiq=42367912) widget layout tool.
 • Updates for the self-updating application were delivered over the internet using [Marimba Castanet](https://www.infoworld.com/article/2076707/marimba-launches-new-castanet-with-a-less-java-centric-focus.html) push-technology.</t>
         </is>
       </c>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>•	Doctor of Philosopy degree, [MIT]{https://shawn.beckerstudio.com/wp-content/uploads/2023/05/MIT-logo.png}, Cambridge, Massachusettes
+          <t>•	Doctor of Philosopy degree, [http://www.MIT]{https://shawn.beckerstudio.com/wp-content/uploads/2023/05/MIT-logo.png}, Cambridge, Massachusettes
 •	Media Laboratory, Media Arts and Sciences
 •	Took courses in machine vision, signals and systems, digital signal processing, and stochastics.
 •	Helped build the operating system for the [Cheops multi-processor system](http://alumni.media.mit.edu/~wad/cheops_CSVT/cheops.html) used for digital video research and for holographic video
@@ -1159,7 +1159,7 @@
 •	“Semiautomatic Camera Lens Calibration from Partially Known Structure”, Shawn Becker, MIT Media Lab Reports, 1994
 •	[“Formulating a scene probability equation to differentiate the effects of shape &amp; albedo on image brightness.”](https://www.researchgate.net/publication/2668457_Formulating_a_Scene_Probability_Equation_to_Differentiate_the_Effects_of_Shape_and_Albedo_on_Image_Brightness) Shawn Becker, MIT Media Lab Reports, 1994
 •	“Computation of some projective-chirplet-transform &amp; metaplectic-chirplet-transform subspaces, with applications in image processing.” Steve Mann &amp; Shawn Becker, DSP World Symposium, Boston, Massachusetts, November 1992.
-• [C programming language], [TclTk], [X11], [HTML], [JavaScript],[CSS],[XMotif], [Bash], [Linux]</t>
+• [C programming language], , [http://X11.com], , [http://JavaScript.com],,, [http://Bash.com], [http://Linux.com]</t>
         </is>
       </c>
     </row>
@@ -1205,14 +1205,14 @@
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>• Masters of Science degree, [BYU]{https://shawn.beckerstudio.com/wp-content/uploads/2023/05/BYU-entrance-150x150.jpg}, Provo, Utah
+          <t>• Masters of Science degree, {https://shawn.beckerstudio.com/wp-content/uploads/2023/05/BYU-entrance-150x150.jpg}, Provo, Utah
 Took all courses required for both bachelors and masters degrees in Computer Science
 • Thesis project [“Interactive Measurement of Three-Dimensional Objects Using a Depth Buffer &amp; Linear Probe.”](https://dl.acm.org/doi/pdf/10.1145/108360.108446) CS MS Thesis, Shawn Becker, William A. Barrett &amp; Dan R. Olsen, ACM Transactions on Graphics, Vol. 10, No. 2, April 1991
 • Top Research Presentation – New Tech Research Conference - BYU – Provo, UT – March 1990
 • [“Fast Automated Object Detection Using Signature Parsing.”](https://www.spiedigitallibrary.org/conference-proceedings-of-spie/1192/1/Fast-Automated-Object-Detection-Using-Signature-Parsing/10.1117/12.969720.short) Tim Heaton; Shawn Becker; Kelley Anderson; William Barrett: Proceedings Volume 1192, Intelligent Robots &amp; Computer Vision VIII: Algorithms &amp; Techniques; (http://www1990.com) https://doi.org/10.1117/12.969720
 • [“Probabilistic Segmentation of Myocardial Tissue by Deterministic Relaxation.”](https://scholarsarchive.byu.edu/cgi/viewcontent.cgi?article=1737&amp;context=facpub) Jerome A. Broekhuijsen, Shawn C. Becker, &amp; William A. Barrett: IEEE Proceedings of Computers in Cardiology, pp. 99-12, Jerusalem, September 1989.
 • [“Interactive Measurement of three-Dimensional Cardiac Morphology.”]{https://shawn.beckerstudio.com/wp-content/uploads/2023/05/BYU-MS-CS-Skull-Cross-Section-1.jpeg}(https://scholarsarchive.byu.edu/cgi/viewcontent.cgi?article=1736&amp;context=facpub) Shawn C Becker, William A Barrett, October 1989, DOI: 10.1109/CIC.1989.130586, Conference: Computers in Cardiology.
-• [C programming language], [Bash], [Linux], [XMotif], and [X11].</t>
+• [C programming language], [http://Bash.com], [http://Linux.com], , and [http://X11.com].</t>
         </is>
       </c>
     </row>
@@ -1258,8 +1258,8 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>• Front-end software developer of a reverse kinametics path planning system for multi-axis industrial robots for [Cimmetrix]{https://shawn.beckerstudio.com/wp-content/uploads/2023/05/Cimetrix-PDF-combined-logo-150x100.png}.
-• Technologies used include [Bash], [Linux], [C programming language], [Bash](https://en.wikipedia.org/wiki/Bourne_shell), [X11] , [Xt toolkit intrinsics](https://en.wikipedia.org/wiki/X_Toolkit_Intrinsics), [Silicon Graphics Irix](https://en.wikipedia.org/wiki/Silicon_Graphics), and [HP-UX](https://en.wikipedia.org/wiki/HP-UX).</t>
+          <t>• Front-end software developer of a reverse kinametics path planning system for multi-axis industrial robots for {https://shawn.beckerstudio.com/wp-content/uploads/2023/05/Cimetrix-PDF-combined-logo-150x100.png}.
+• Technologies used include [http://Bash.com], [http://Linux.com], [C programming language], [http://Bash.com](https://en.wikipedia.org/wiki/Bourne_shell), [http://X11.com] , [Xt toolkit intrinsics](https://en.wikipedia.org/wiki/X_Toolkit_Intrinsics), [Silicon Graphics Irix](https://en.wikipedia.org/wiki/Silicon_Graphics), and (https://en.wikipedia.org/wiki/HP-UX).</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t xml:space="preserve">• MSC, now called [OneCall](https://onecallcm.com/), is a leading workers compensation services company. 
+          <t xml:space="preserve">• MSC, now called (https://onecallcm.com/), is a leading workers compensation services company. 
 • As project manager and technical lead for this Sierra Vista Group project, I presented fixed schedule-fixed budget project proposals to C-level executives to add features to their legacy call center system used by 10 different healthcare divisions. 
 • Interviewed stakeholders to create functional requirements and technical spefications for each stage of development.
 • Worked with development team to create work plan, assign tasks.
@@ -1356,8 +1356,8 @@
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t xml:space="preserve">• [Eleven LLC](https://www.eleven.net/) built mobile apps used by beverage industry distributors to help manage placement  of their products in the shelves and coolers in retail locations. The work done by the Sierra Vista Group was instrumental in their company being acquired by [Trimble](https://help.trimblegeospatial.com/TMM/Home.htm). 
-• As the architect and team lead, we used [Java], [Bash], [GitHub], [Linux], and  [JBoss](https://developers.redhat.com/products/eap/overview) message-oriented middleware platform, [Sybase Anywhere](https://texas.gs.shi.com/Product/30451452/Sybase-SQL-Anywhere-Advanced-Edition) for the client/server based database, and [Windows Mobile](https://en.wikipedia.org/wiki/Windows_Mobile_5.0) running on ruggedized mobile devices. </t>
+          <t xml:space="preserve">• [Eleven LLC](https://www.eleven.net/) built mobile apps used by beverage industry distributors to help manage placement  of their products in the shelves and coolers in retail locations. The work done by the Sierra Vista Group was instrumental in their company being acquired by [http://Trimble.com](https://help.trimblegeospatial.com/TMM/Home.htm). 
+• As the architect and team lead, we used , [http://Bash.com], [http://GitHub.com], [http://Linux.com], and  [http://JBoss.com](https://developers.redhat.com/products/eap/overview) message-oriented middleware platform, [Sybase Anywhere](https://texas.gs.shi.com/Product/30451452/Sybase-SQL-Anywhere-Advanced-Edition) for the client/server based database, and [Windows Mobile](https://en.wikipedia.org/wiki/Windows_Mobile_5.0) running on ruggedized mobile devices. </t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
         <is>
           <t>• [Intrusic LLC](https://www.crunchbase.com/organization/intrusic) built real-time network monitoring systems that identified external and internal network intrusion attempts
 • As a Sierra Vista Group architech, I helped design and develop an approach for buffering live streaming network traffic for asynchronous package processing. 
-• Used [Linux](https://www.debian.org/), [C programming language](https://www.cprogramming.com/books/ritchie.html), and [Visio](https://www.microsoft.com/en-us/microsoft-365/visio/flowchart-software).</t>
+• Used [http://Linux.com](https://www.debian.org/), [C programming language](https://www.cprogramming.com/books/ritchie.html), and [http://Visio.com](https://www.microsoft.com/en-us/microsoft-365/visio/flowchart-software).</t>
         </is>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
         <is>
           <t>•  AMI (https://amientertainment.com/) was the internet-music distribution incarnation of Rowe International.  
 •  As a Sierra Vista Group project manager and technical lead, I helped design and implement their system for making monthly ACH royalty payments to music copyright owners for mechanical and performance licensing rights.
-•  Used [FileMaker Pro](https://www.claris.com/filemaker/), [Bash], [Linux], [HTML], [CSS], [JavaScript], [Java], and [Visio](https://www.microsoft.com/en-us/microsoft-365/visio/flowchart-software).</t>
+•  Used [FileMaker Pro](https://www.claris.com/filemaker/), [http://Bash.com], [http://Linux.com], , , [http://JavaScript.com], , and [http://Visio.com](https://www.microsoft.com/en-us/microsoft-365/visio/flowchart-software).</t>
         </is>
       </c>
     </row>
@@ -1502,7 +1502,7 @@
           <t xml:space="preserve">•  [Rowe International](https://pitchbook.com/profiles/company/13178-08) was the leading manufacturer of music jukeboxes. 
 •  Sierra Vista Group was consulted to assess their available technologies and create a plan to build their back-end systems to let them become a leading provider of internet-based music.
 •  As project manager and technical lead created the project plan and led the development of a full-stack web application used by  jukebox owners and Rowe sales and marketing.
-•  Used [Java], [Bash], [Linux], [HTML], [CSS], [JavaScript], [ObjectDesign](https://object.design/), [MySQL](https://www.mysql.com/), and [Adobe Photoshop](https://www.adobe.com/products/photoshop.html). 
+•  Used , [http://Bash.com], [http://Linux.com], , , [http://JavaScript.com], [http://ObjectDesign.com](https://object.design/), [http://MySQL.com](https://www.mysql.com/), and [Adobe Photoshop](https://www.adobe.com/products/photoshop.html). 
 </t>
         </is>
       </c>
